--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -33,6 +33,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -225,6 +232,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>报关申报价（</t>
     </r>
     <r>
@@ -1683,7 +1696,7 @@
       <c r="CD2" s="18"/>
     </row>
   </sheetData>
-  <dataValidations count="19">
+  <dataValidations count="18">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
@@ -1739,10 +1752,6 @@
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+21</formula2>
-    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL3:BL1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>spu</t>
   </si>
@@ -229,6 +229,9 @@
   <si>
     <t xml:space="preserve">报关产品属性
 </t>
+  </si>
+  <si>
+    <t>保险属性</t>
   </si>
   <si>
     <r>
@@ -1047,10 +1050,10 @@
     <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1372,7 +1375,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CD2"/>
+  <dimension ref="A1:CE2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -1426,23 +1429,23 @@
     <col min="59" max="59" width="10.25" customWidth="1"/>
     <col min="60" max="60" width="9.375" customWidth="1"/>
     <col min="61" max="61" width="12.75" customWidth="1"/>
-    <col min="62" max="62" width="12.75" style="2" customWidth="1"/>
-    <col min="63" max="63" width="13.75" customWidth="1"/>
-    <col min="64" max="64" width="13.375" customWidth="1"/>
-    <col min="65" max="65" width="11.75" customWidth="1"/>
-    <col min="66" max="66" width="9.875" customWidth="1"/>
-    <col min="67" max="67" width="10" customWidth="1"/>
-    <col min="68" max="68" width="11" customWidth="1"/>
-    <col min="69" max="69" width="9.375"/>
-    <col min="71" max="71" width="11.875" style="7" customWidth="1"/>
-    <col min="72" max="72" width="12.5" style="7" customWidth="1"/>
-    <col min="73" max="73" width="12.125" style="7" customWidth="1"/>
-    <col min="74" max="79" width="9" style="7"/>
-    <col min="80" max="80" width="9" style="6"/>
-    <col min="81" max="82" width="11.125" style="8" customWidth="1"/>
+    <col min="62" max="63" width="12.75" style="2" customWidth="1"/>
+    <col min="64" max="64" width="13.75" customWidth="1"/>
+    <col min="65" max="65" width="13.375" customWidth="1"/>
+    <col min="66" max="66" width="11.75" customWidth="1"/>
+    <col min="67" max="67" width="9.875" customWidth="1"/>
+    <col min="68" max="68" width="10" customWidth="1"/>
+    <col min="69" max="69" width="11" customWidth="1"/>
+    <col min="70" max="70" width="9.375"/>
+    <col min="72" max="72" width="11.875" style="7" customWidth="1"/>
+    <col min="73" max="73" width="12.5" style="7" customWidth="1"/>
+    <col min="74" max="74" width="12.125" style="7" customWidth="1"/>
+    <col min="75" max="80" width="9" style="7"/>
+    <col min="81" max="81" width="9" style="6"/>
+    <col min="82" max="83" width="11.125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:82">
+    <row r="1" s="1" customFormat="1" spans="1:83">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1629,7 +1632,7 @@
       <c r="BJ1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="9" t="s">
+      <c r="BK1" s="11" t="s">
         <v>62</v>
       </c>
       <c r="BL1" s="9" t="s">
@@ -1641,10 +1644,10 @@
       <c r="BN1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="16" t="s">
+      <c r="BO1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="9" t="s">
+      <c r="BP1" s="16" t="s">
         <v>67</v>
       </c>
       <c r="BQ1" s="9" t="s">
@@ -1653,7 +1656,7 @@
       <c r="BR1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="17" t="s">
+      <c r="BS1" s="9" t="s">
         <v>70</v>
       </c>
       <c r="BT1" s="17" t="s">
@@ -1680,27 +1683,30 @@
       <c r="CA1" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="14" t="s">
+      <c r="CB1" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="19" t="s">
+      <c r="CC1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="19" t="s">
+      <c r="CD1" s="18" t="s">
         <v>81</v>
       </c>
+      <c r="CE1" s="18" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="2" spans="80:82">
-      <c r="CB2" s="18"/>
-      <c r="CC2" s="18"/>
-      <c r="CD2" s="18"/>
+    <row r="2" spans="81:83">
+      <c r="CC2" s="19"/>
+      <c r="CD2" s="19"/>
+      <c r="CE2" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="18">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BJ$1:BJ$1048576 BU$1:BV$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV$1:BW$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1708,7 +1714,7 @@
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BY$1:BY$1048576 BA3:BB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BZ$1:BZ$1048576 BA3:BB1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
@@ -1724,7 +1730,7 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BW$1:BW$1048576 BS$1:BT$1048576 BZ$1:CA$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX$1:BX$1048576 BT$1:BU$1048576 CA$1:CB$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
@@ -1736,7 +1742,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BX$1:BX$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY$1:BY$1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
@@ -1744,7 +1750,7 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CB$1:CB$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC$1:CC$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1752,15 +1758,15 @@
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL3:BL1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM3:BM1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ3:BQ1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BS3:BS1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
@@ -285,22 +285,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)</t>
-  </si>
-  <si>
-    <t>箱规(长)</t>
-  </si>
-  <si>
-    <t>箱规(宽)</t>
-  </si>
-  <si>
-    <t>箱规(高)</t>
+    <t>产品尺寸(长)(cm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)(cm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)(cm)</t>
+  </si>
+  <si>
+    <t>箱规(长)(cm)</t>
+  </si>
+  <si>
+    <t>箱规(宽)(cm)</t>
+  </si>
+  <si>
+    <t>箱规(高)(cm)</t>
   </si>
   <si>
     <t>毛重</t>
@@ -1706,7 +1706,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV$1:BW$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1730,7 +1730,7 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX$1:BX$1048576 BT$1:BU$1048576 CA$1:CB$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 CA$1:CB$1048576 BT2:BU1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
@@ -1742,7 +1742,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY$1:BY$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
@@ -285,22 +285,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(长)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(宽)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(高)(cm)</t>
+    <t>产品尺寸(长)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)</t>
+  </si>
+  <si>
+    <t>箱规(长)</t>
+  </si>
+  <si>
+    <t>箱规(宽)</t>
+  </si>
+  <si>
+    <t>箱规(高)</t>
   </si>
   <si>
     <t>毛重</t>
@@ -1706,7 +1706,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV$1:BW$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1730,7 +1730,7 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 CA$1:CB$1048576 BT2:BU1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX$1:BX$1048576 BT$1:BU$1048576 CA$1:CB$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
@@ -1742,7 +1742,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY$1:BY$1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -303,13 +303,13 @@
     <t>箱规(高)(cm)</t>
   </si>
   <si>
-    <t>毛重</t>
-  </si>
-  <si>
-    <t>净重</t>
-  </si>
-  <si>
-    <t>单箱重量</t>
+    <t>毛重(g)</t>
+  </si>
+  <si>
+    <t>净重(g)</t>
+  </si>
+  <si>
+    <t>单箱重量(kg)</t>
   </si>
   <si>
     <t>单箱数量</t>
@@ -1714,7 +1714,7 @@
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BZ$1:BZ$1048576 BA3:BB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BZ2:BZ1048576 BA3:BB1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
@@ -1730,7 +1730,7 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 CA$1:CB$1048576 BT2:BU1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 BT2:BU1048576 CA2:CB1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -325,16 +325,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
     <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
-    <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -995,7 +994,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1011,18 +1010,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1038,22 +1034,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1375,8 +1368,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CE2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:CE1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -1442,110 +1435,110 @@
     <col min="74" max="74" width="12.125" style="7" customWidth="1"/>
     <col min="75" max="80" width="9" style="7"/>
     <col min="81" max="81" width="9" style="6"/>
-    <col min="82" max="83" width="11.125" style="8" customWidth="1"/>
+    <col min="82" max="83" width="11.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:83">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="W1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="X1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Y1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="Z1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AA1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AB1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AC1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AD1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AE1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AF1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AG1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AH1" s="13" t="s">
         <v>33</v>
       </c>
       <c r="AI1" s="14" t="s">
@@ -1563,100 +1556,100 @@
       <c r="AM1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="12" t="s">
+      <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="12" t="s">
+      <c r="AO1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="12" t="s">
+      <c r="AP1" s="11" t="s">
         <v>41</v>
       </c>
       <c r="AQ1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="9" t="s">
+      <c r="AR1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="9" t="s">
+      <c r="AS1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="9" t="s">
+      <c r="AT1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="9" t="s">
+      <c r="AU1" s="8" t="s">
         <v>46</v>
       </c>
       <c r="AV1" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="11" t="s">
+      <c r="AW1" s="10" t="s">
         <v>48</v>
       </c>
       <c r="AX1" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="11" t="s">
+      <c r="AY1" s="10" t="s">
         <v>50</v>
       </c>
       <c r="AZ1" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="9" t="s">
+      <c r="BA1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="9" t="s">
+      <c r="BB1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="9" t="s">
+      <c r="BC1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="12" t="s">
+      <c r="BD1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="9" t="s">
+      <c r="BE1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="9" t="s">
+      <c r="BF1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="9" t="s">
+      <c r="BG1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="9" t="s">
+      <c r="BH1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="9" t="s">
+      <c r="BI1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="11" t="s">
+      <c r="BJ1" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="11" t="s">
+      <c r="BK1" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="9" t="s">
+      <c r="BL1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="9" t="s">
+      <c r="BM1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="9" t="s">
+      <c r="BN1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="9" t="s">
+      <c r="BO1" s="8" t="s">
         <v>66</v>
       </c>
       <c r="BP1" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="9" t="s">
+      <c r="BQ1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="9" t="s">
+      <c r="BR1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="9" t="s">
+      <c r="BS1" s="8" t="s">
         <v>70</v>
       </c>
       <c r="BT1" s="17" t="s">
@@ -1689,58 +1682,57 @@
       <c r="CC1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="18" t="s">
+      <c r="CD1" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="18" t="s">
+      <c r="CE1" s="13" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="81:83">
-      <c r="CC2" s="19"/>
-      <c r="CD2" s="19"/>
-      <c r="CE2" s="19"/>
     </row>
   </sheetData>
-  <dataValidations count="18">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
+  <dataValidations count="13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 J2:J1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 AP1 W2:W1048576 AP2:AP1048576 BD2:BD1048576">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AM1 AI2:AI1048576 AM2:AM1048576 AV2:AV1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1:AL1 AQ1 AQ2:AQ1048576 AJ2:AL1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN1:AO1 AN2:AO1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK1 R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK2:BK1048576 BV2:BW1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 Z2:Z1048576 AC2:AD1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC1 AZ2:AZ1048576 CC2:CC1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AC2:AD1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BZ2:BZ1048576 BA3:BB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576 AE2:AE1048576">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576 BZ2:BZ1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576 BC3:BC1048576">
-      <formula1>0</formula1>
-      <formula2>9999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576 AP$1:AP$1048576 BD2:BD1048576">
-      <formula1>1</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576 AA2:AA1048576 AE2:AE1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 BT2:BU1048576 CA2:CB1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576 AV2:AV1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AQ$1048576 AJ$1:AL$1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
       <formula1>0</formula1>
@@ -1750,35 +1742,12 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC$1:CC$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF3:BF1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+23</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM3:BM1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900000</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR1048576">
-      <formula1>25569</formula1>
-      <formula2>72686</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BS3:BS1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AX3:AX1048573" listDataValidation="1"/>
+    <ignoredError sqref="AX2:AX1048572" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -1691,36 +1691,20 @@
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 J2:J1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 AP1 W2:W1048576 AP2:AP1048576 BD2:BD1048576">
-      <formula1>1</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AM1 AI2:AI1048576 AM2:AM1048576 AV2:AV1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1:AL1 AQ1 AQ2:AQ1048576 AJ2:AL1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN1:AO1 AN2:AO1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK1 R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK2:BK1048576 BV2:BW1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC1 AZ2:AZ1048576 CC2:CC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AC2:AD1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576 AP$1:AP$1048576 BD2:BD1048576">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576 AE2:AE1048576">
       <formula1>0</formula1>
@@ -1734,6 +1718,14 @@
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576 AV2:AV1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AQ$1048576 AJ$1:AL$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
@@ -1741,6 +1733,14 @@
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC$1:CC$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -1691,20 +1691,36 @@
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 J2:J1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 AP1 W2:W1048576 AP2:AP1048576 BD2:BD1048576">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AM1 AI2:AI1048576 AM2:AM1048576 AV2:AV1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1:AL1 AQ1 AQ2:AQ1048576 AJ2:AL1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN1:AO1 AN2:AO1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK1 R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK2:BK1048576 BV2:BW1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC1 AZ2:AZ1048576 CC2:CC1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AC2:AD1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576 AP$1:AP$1048576 BD2:BD1048576">
-      <formula1>1</formula1>
-      <formula2>2958464</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576 AE2:AE1048576">
       <formula1>0</formula1>
@@ -1718,14 +1734,6 @@
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576 AV2:AV1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AQ$1048576 AJ$1:AL$1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
@@ -1734,20 +1742,12 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC$1:CC$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AX2:AX1048572" listDataValidation="1"/>
+    <ignoredError sqref="AX2:AX1048565" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>spu</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>品牌</t>
+  </si>
+  <si>
+    <t>研发团队</t>
   </si>
   <si>
     <t>产品开发状态</t>
@@ -1368,7 +1371,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CE1"/>
+  <dimension ref="A1:CF1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -1378,67 +1381,67 @@
     <col min="11" max="11" width="12.375" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="7.75" customWidth="1"/>
-    <col min="14" max="14" width="12.75" customWidth="1"/>
-    <col min="17" max="17" width="11.5" customWidth="1"/>
-    <col min="18" max="18" width="12.125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="14.375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="15.375" customWidth="1"/>
-    <col min="21" max="21" width="15.875" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="12" style="3" customWidth="1"/>
-    <col min="24" max="24" width="16.625" customWidth="1"/>
-    <col min="25" max="25" width="5.875" customWidth="1"/>
-    <col min="26" max="26" width="9.75" customWidth="1"/>
-    <col min="27" max="27" width="15.125" style="4" customWidth="1"/>
-    <col min="28" max="28" width="15" style="2" customWidth="1"/>
-    <col min="29" max="29" width="14.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="8.75" style="2" customWidth="1"/>
-    <col min="31" max="31" width="15.25" style="2" customWidth="1"/>
-    <col min="32" max="32" width="16.75" style="2" customWidth="1"/>
-    <col min="33" max="33" width="14" style="2" customWidth="1"/>
-    <col min="34" max="34" width="11.5" style="5"/>
-    <col min="35" max="35" width="13" style="6" customWidth="1"/>
-    <col min="36" max="36" width="12.25" style="6" customWidth="1"/>
-    <col min="37" max="37" width="11.125" style="6" customWidth="1"/>
-    <col min="38" max="38" width="13.625" style="6" customWidth="1"/>
-    <col min="39" max="39" width="12.625" style="6" customWidth="1"/>
-    <col min="40" max="40" width="14.25" style="3" customWidth="1"/>
-    <col min="41" max="41" width="14.5" style="3" customWidth="1"/>
-    <col min="42" max="42" width="12" style="3" customWidth="1"/>
-    <col min="43" max="43" width="10.75" style="6" customWidth="1"/>
-    <col min="45" max="45" width="10.75" customWidth="1"/>
-    <col min="46" max="46" width="16.375" customWidth="1"/>
-    <col min="47" max="47" width="12.375" customWidth="1"/>
-    <col min="48" max="48" width="11.5" style="6" customWidth="1"/>
-    <col min="49" max="49" width="15.875" style="2" customWidth="1"/>
-    <col min="50" max="50" width="11.625" style="6" customWidth="1"/>
-    <col min="51" max="51" width="15.875" style="2" customWidth="1"/>
-    <col min="52" max="52" width="13.5" style="6" customWidth="1"/>
-    <col min="54" max="54" width="11.75" customWidth="1"/>
-    <col min="55" max="55" width="12" customWidth="1"/>
-    <col min="56" max="56" width="11" style="3" customWidth="1"/>
-    <col min="57" max="57" width="9.125" customWidth="1"/>
-    <col min="58" max="58" width="21.5" customWidth="1"/>
-    <col min="59" max="59" width="10.25" customWidth="1"/>
-    <col min="60" max="60" width="9.375" customWidth="1"/>
-    <col min="61" max="61" width="12.75" customWidth="1"/>
-    <col min="62" max="63" width="12.75" style="2" customWidth="1"/>
-    <col min="64" max="64" width="13.75" customWidth="1"/>
-    <col min="65" max="65" width="13.375" customWidth="1"/>
-    <col min="66" max="66" width="11.75" customWidth="1"/>
-    <col min="67" max="67" width="9.875" customWidth="1"/>
-    <col min="68" max="68" width="10" customWidth="1"/>
-    <col min="69" max="69" width="11" customWidth="1"/>
-    <col min="70" max="70" width="9.375"/>
-    <col min="72" max="72" width="11.875" style="7" customWidth="1"/>
-    <col min="73" max="73" width="12.5" style="7" customWidth="1"/>
-    <col min="74" max="74" width="12.125" style="7" customWidth="1"/>
-    <col min="75" max="80" width="9" style="7"/>
-    <col min="81" max="81" width="9" style="6"/>
-    <col min="82" max="83" width="11.125" style="5" customWidth="1"/>
+    <col min="14" max="15" width="12.75" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="12.125" style="2" customWidth="1"/>
+    <col min="20" max="20" width="14.375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="15.375" customWidth="1"/>
+    <col min="22" max="22" width="15.875" customWidth="1"/>
+    <col min="23" max="23" width="11" customWidth="1"/>
+    <col min="24" max="24" width="12" style="3" customWidth="1"/>
+    <col min="25" max="25" width="16.625" customWidth="1"/>
+    <col min="26" max="26" width="5.875" customWidth="1"/>
+    <col min="27" max="27" width="9.75" customWidth="1"/>
+    <col min="28" max="28" width="15.125" style="4" customWidth="1"/>
+    <col min="29" max="29" width="15" style="2" customWidth="1"/>
+    <col min="30" max="30" width="14.875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="8.75" style="2" customWidth="1"/>
+    <col min="32" max="32" width="15.25" style="2" customWidth="1"/>
+    <col min="33" max="33" width="16.75" style="2" customWidth="1"/>
+    <col min="34" max="34" width="14" style="2" customWidth="1"/>
+    <col min="35" max="35" width="11.5" style="5"/>
+    <col min="36" max="36" width="13" style="6" customWidth="1"/>
+    <col min="37" max="37" width="12.25" style="6" customWidth="1"/>
+    <col min="38" max="38" width="11.125" style="6" customWidth="1"/>
+    <col min="39" max="39" width="13.625" style="6" customWidth="1"/>
+    <col min="40" max="40" width="12.625" style="6" customWidth="1"/>
+    <col min="41" max="41" width="14.25" style="3" customWidth="1"/>
+    <col min="42" max="42" width="14.5" style="3" customWidth="1"/>
+    <col min="43" max="43" width="12" style="3" customWidth="1"/>
+    <col min="44" max="44" width="10.75" style="6" customWidth="1"/>
+    <col min="46" max="46" width="10.75" customWidth="1"/>
+    <col min="47" max="47" width="16.375" customWidth="1"/>
+    <col min="48" max="48" width="12.375" customWidth="1"/>
+    <col min="49" max="49" width="11.5" style="6" customWidth="1"/>
+    <col min="50" max="50" width="15.875" style="2" customWidth="1"/>
+    <col min="51" max="51" width="11.625" style="6" customWidth="1"/>
+    <col min="52" max="52" width="15.875" style="2" customWidth="1"/>
+    <col min="53" max="53" width="13.5" style="6" customWidth="1"/>
+    <col min="55" max="55" width="11.75" customWidth="1"/>
+    <col min="56" max="56" width="12" customWidth="1"/>
+    <col min="57" max="57" width="11" style="3" customWidth="1"/>
+    <col min="58" max="58" width="9.125" customWidth="1"/>
+    <col min="59" max="59" width="21.5" customWidth="1"/>
+    <col min="60" max="60" width="10.25" customWidth="1"/>
+    <col min="61" max="61" width="9.375" customWidth="1"/>
+    <col min="62" max="62" width="12.75" customWidth="1"/>
+    <col min="63" max="64" width="12.75" style="2" customWidth="1"/>
+    <col min="65" max="65" width="13.75" customWidth="1"/>
+    <col min="66" max="66" width="13.375" customWidth="1"/>
+    <col min="67" max="67" width="11.75" customWidth="1"/>
+    <col min="68" max="68" width="9.875" customWidth="1"/>
+    <col min="69" max="69" width="10" customWidth="1"/>
+    <col min="70" max="70" width="11" customWidth="1"/>
+    <col min="71" max="71" width="9.375"/>
+    <col min="73" max="73" width="11.875" style="7" customWidth="1"/>
+    <col min="74" max="74" width="12.5" style="7" customWidth="1"/>
+    <col min="75" max="75" width="12.125" style="7" customWidth="1"/>
+    <col min="76" max="81" width="9" style="7"/>
+    <col min="82" max="82" width="9" style="6"/>
+    <col min="83" max="84" width="11.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:83">
+    <row r="1" s="1" customFormat="1" spans="1:84">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1490,13 +1493,13 @@
       <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="10" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="8" t="s">
@@ -1505,10 +1508,10 @@
       <c r="V1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="W1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="X1" s="11" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="8" t="s">
@@ -1517,10 +1520,10 @@
       <c r="Z1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="12" t="s">
+      <c r="AA1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AB1" s="12" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="10" t="s">
@@ -1538,10 +1541,10 @@
       <c r="AG1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="13" t="s">
+      <c r="AH1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="14" t="s">
+      <c r="AI1" s="13" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="14" t="s">
@@ -1553,10 +1556,10 @@
       <c r="AL1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="15" t="s">
+      <c r="AM1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="11" t="s">
+      <c r="AN1" s="15" t="s">
         <v>39</v>
       </c>
       <c r="AO1" s="11" t="s">
@@ -1565,10 +1568,10 @@
       <c r="AP1" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="14" t="s">
+      <c r="AQ1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="8" t="s">
+      <c r="AR1" s="14" t="s">
         <v>43</v>
       </c>
       <c r="AS1" s="8" t="s">
@@ -1580,22 +1583,22 @@
       <c r="AU1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="14" t="s">
+      <c r="AV1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="10" t="s">
+      <c r="AW1" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="14" t="s">
+      <c r="AX1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="10" t="s">
+      <c r="AY1" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="14" t="s">
+      <c r="AZ1" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="8" t="s">
+      <c r="BA1" s="14" t="s">
         <v>52</v>
       </c>
       <c r="BB1" s="8" t="s">
@@ -1604,10 +1607,10 @@
       <c r="BC1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="11" t="s">
+      <c r="BD1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="8" t="s">
+      <c r="BE1" s="11" t="s">
         <v>56</v>
       </c>
       <c r="BF1" s="8" t="s">
@@ -1622,13 +1625,13 @@
       <c r="BI1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="10" t="s">
+      <c r="BJ1" s="8" t="s">
         <v>61</v>
       </c>
       <c r="BK1" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="8" t="s">
+      <c r="BL1" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BM1" s="8" t="s">
@@ -1640,10 +1643,10 @@
       <c r="BO1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="16" t="s">
+      <c r="BP1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="8" t="s">
+      <c r="BQ1" s="16" t="s">
         <v>68</v>
       </c>
       <c r="BR1" s="8" t="s">
@@ -1652,7 +1655,7 @@
       <c r="BS1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="17" t="s">
+      <c r="BT1" s="8" t="s">
         <v>71</v>
       </c>
       <c r="BU1" s="17" t="s">
@@ -1679,75 +1682,78 @@
       <c r="CB1" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="14" t="s">
+      <c r="CC1" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="13" t="s">
+      <c r="CD1" s="14" t="s">
         <v>81</v>
       </c>
       <c r="CE1" s="13" t="s">
         <v>82</v>
+      </c>
+      <c r="CF1" s="13" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 J2:J1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 AP1 W2:W1048576 AP2:AP1048576 BD2:BD1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AH2:AH1048576 AZ2:AZ1048576 BL$1:BL$1048576 BW2:BX1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 AD2:AE1048576">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576 AQ$1:AQ$1048576 BE2:BE1048576">
       <formula1>1</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AM1 AI2:AI1048576 AM2:AM1048576 AV2:AV1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576 AF2:AF1048576">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 CA2:CA1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576 BY2:BY1048576 BU2:BV1048576 CB2:CC1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1:AL1 AQ1 AQ2:AQ1048576 AJ2:AL1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ$1:AJ$1048576 AN$1:AN$1048576 AW2:AW1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR$1:AR$1048576 AK$1:AM$1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN1:AO1 AN2:AO1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576 BZ2:BZ1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK1 R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK2:BK1048576 BV2:BW1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576 CD$1:CD$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC1 AZ2:AZ1048576 CC2:CC1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AC2:AD1048576">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576 AE2:AE1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576 BZ2:BZ1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 BT2:BU1048576 CA2:CB1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999</formula2>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO$1:AP$1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AX2:AX1048565" listDataValidation="1"/>
+    <ignoredError sqref="AY2:AY1048565" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>spu</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>保险属性</t>
+  </si>
+  <si>
+    <t>电池重量（g）</t>
   </si>
   <si>
     <r>
@@ -1371,7 +1374,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CF1"/>
+  <dimension ref="A1:CG1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -1425,23 +1428,23 @@
     <col min="60" max="60" width="10.25" customWidth="1"/>
     <col min="61" max="61" width="9.375" customWidth="1"/>
     <col min="62" max="62" width="12.75" customWidth="1"/>
-    <col min="63" max="64" width="12.75" style="2" customWidth="1"/>
-    <col min="65" max="65" width="13.75" customWidth="1"/>
-    <col min="66" max="66" width="13.375" customWidth="1"/>
-    <col min="67" max="67" width="11.75" customWidth="1"/>
-    <col min="68" max="68" width="9.875" customWidth="1"/>
-    <col min="69" max="69" width="10" customWidth="1"/>
-    <col min="70" max="70" width="11" customWidth="1"/>
-    <col min="71" max="71" width="9.375"/>
-    <col min="73" max="73" width="11.875" style="7" customWidth="1"/>
-    <col min="74" max="74" width="12.5" style="7" customWidth="1"/>
-    <col min="75" max="75" width="12.125" style="7" customWidth="1"/>
-    <col min="76" max="81" width="9" style="7"/>
-    <col min="82" max="82" width="9" style="6"/>
-    <col min="83" max="84" width="11.125" style="5" customWidth="1"/>
+    <col min="63" max="65" width="12.75" style="2" customWidth="1"/>
+    <col min="66" max="66" width="13.75" customWidth="1"/>
+    <col min="67" max="67" width="13.375" customWidth="1"/>
+    <col min="68" max="68" width="11.75" customWidth="1"/>
+    <col min="69" max="69" width="9.875" customWidth="1"/>
+    <col min="70" max="70" width="10" customWidth="1"/>
+    <col min="71" max="71" width="11" customWidth="1"/>
+    <col min="72" max="72" width="9.375"/>
+    <col min="74" max="74" width="11.875" style="7" customWidth="1"/>
+    <col min="75" max="75" width="12.5" style="7" customWidth="1"/>
+    <col min="76" max="76" width="12.125" style="7" customWidth="1"/>
+    <col min="77" max="82" width="9" style="7"/>
+    <col min="83" max="83" width="9" style="6"/>
+    <col min="84" max="85" width="11.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:84">
+    <row r="1" s="1" customFormat="1" spans="1:85">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1634,7 +1637,7 @@
       <c r="BL1" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="8" t="s">
+      <c r="BM1" s="10" t="s">
         <v>64</v>
       </c>
       <c r="BN1" s="8" t="s">
@@ -1646,10 +1649,10 @@
       <c r="BP1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="16" t="s">
+      <c r="BQ1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="8" t="s">
+      <c r="BR1" s="16" t="s">
         <v>69</v>
       </c>
       <c r="BS1" s="8" t="s">
@@ -1658,7 +1661,7 @@
       <c r="BT1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="17" t="s">
+      <c r="BU1" s="8" t="s">
         <v>72</v>
       </c>
       <c r="BV1" s="17" t="s">
@@ -1685,14 +1688,17 @@
       <c r="CC1" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="14" t="s">
+      <c r="CD1" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="13" t="s">
+      <c r="CE1" s="14" t="s">
         <v>82</v>
       </c>
       <c r="CF1" s="13" t="s">
         <v>83</v>
+      </c>
+      <c r="CG1" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1700,7 +1706,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AH2:AH1048576 AZ2:AZ1048576 BL$1:BL$1048576 BW2:BX1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AH2:AH1048576 AZ2:AZ1048576 BM$1:BM$1048576 BX2:BY1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1716,11 +1722,11 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 CA2:CA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 CB2:CB1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576 BY2:BY1048576 BU2:BV1048576 CB2:CC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576 BZ2:BZ1048576 BV2:BW1048576 CC2:CD1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
@@ -1732,7 +1738,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576 BZ2:BZ1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576 CA2:CA1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
@@ -1740,7 +1746,7 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576 CD$1:CD$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576 CE$1:CE$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -86,7 +86,7 @@
     <t>品牌</t>
   </si>
   <si>
-    <t>研发团队</t>
+    <t>研发团队（产线）</t>
   </si>
   <si>
     <t>产品开发状态</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -288,22 +288,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(长)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(宽)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(高)(cm)</t>
+    <t>产品尺寸(长)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(长)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(宽)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(高)(mm)</t>
   </si>
   <si>
     <t>毛重(g)</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -291,22 +291,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(长)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(宽)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(高)(cm)</t>
+    <t>产品尺寸(长)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(长)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(宽)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(高)(mm)</t>
   </si>
   <si>
     <t>毛重(g)</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>spu</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>研发团队（产线）</t>
+  </si>
+  <si>
+    <t>BU线</t>
   </si>
   <si>
     <t>产品开发状态</t>
@@ -1374,7 +1377,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CG1"/>
+  <dimension ref="A1:CH1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -1384,67 +1387,67 @@
     <col min="11" max="11" width="12.375" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="7.75" customWidth="1"/>
-    <col min="14" max="15" width="12.75" customWidth="1"/>
-    <col min="18" max="18" width="11.5" customWidth="1"/>
-    <col min="19" max="19" width="12.125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="14.375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="15.375" customWidth="1"/>
-    <col min="22" max="22" width="15.875" customWidth="1"/>
-    <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="12" style="3" customWidth="1"/>
-    <col min="25" max="25" width="16.625" customWidth="1"/>
-    <col min="26" max="26" width="5.875" customWidth="1"/>
-    <col min="27" max="27" width="9.75" customWidth="1"/>
-    <col min="28" max="28" width="15.125" style="4" customWidth="1"/>
-    <col min="29" max="29" width="15" style="2" customWidth="1"/>
-    <col min="30" max="30" width="14.875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="8.75" style="2" customWidth="1"/>
-    <col min="32" max="32" width="15.25" style="2" customWidth="1"/>
-    <col min="33" max="33" width="16.75" style="2" customWidth="1"/>
-    <col min="34" max="34" width="14" style="2" customWidth="1"/>
-    <col min="35" max="35" width="11.5" style="5"/>
-    <col min="36" max="36" width="13" style="6" customWidth="1"/>
-    <col min="37" max="37" width="12.25" style="6" customWidth="1"/>
-    <col min="38" max="38" width="11.125" style="6" customWidth="1"/>
-    <col min="39" max="39" width="13.625" style="6" customWidth="1"/>
-    <col min="40" max="40" width="12.625" style="6" customWidth="1"/>
-    <col min="41" max="41" width="14.25" style="3" customWidth="1"/>
-    <col min="42" max="42" width="14.5" style="3" customWidth="1"/>
-    <col min="43" max="43" width="12" style="3" customWidth="1"/>
-    <col min="44" max="44" width="10.75" style="6" customWidth="1"/>
-    <col min="46" max="46" width="10.75" customWidth="1"/>
-    <col min="47" max="47" width="16.375" customWidth="1"/>
-    <col min="48" max="48" width="12.375" customWidth="1"/>
-    <col min="49" max="49" width="11.5" style="6" customWidth="1"/>
-    <col min="50" max="50" width="15.875" style="2" customWidth="1"/>
-    <col min="51" max="51" width="11.625" style="6" customWidth="1"/>
-    <col min="52" max="52" width="15.875" style="2" customWidth="1"/>
-    <col min="53" max="53" width="13.5" style="6" customWidth="1"/>
-    <col min="55" max="55" width="11.75" customWidth="1"/>
-    <col min="56" max="56" width="12" customWidth="1"/>
-    <col min="57" max="57" width="11" style="3" customWidth="1"/>
-    <col min="58" max="58" width="9.125" customWidth="1"/>
-    <col min="59" max="59" width="21.5" customWidth="1"/>
-    <col min="60" max="60" width="10.25" customWidth="1"/>
-    <col min="61" max="61" width="9.375" customWidth="1"/>
-    <col min="62" max="62" width="12.75" customWidth="1"/>
-    <col min="63" max="65" width="12.75" style="2" customWidth="1"/>
-    <col min="66" max="66" width="13.75" customWidth="1"/>
-    <col min="67" max="67" width="13.375" customWidth="1"/>
-    <col min="68" max="68" width="11.75" customWidth="1"/>
-    <col min="69" max="69" width="9.875" customWidth="1"/>
-    <col min="70" max="70" width="10" customWidth="1"/>
-    <col min="71" max="71" width="11" customWidth="1"/>
-    <col min="72" max="72" width="9.375"/>
-    <col min="74" max="74" width="11.875" style="7" customWidth="1"/>
-    <col min="75" max="75" width="12.5" style="7" customWidth="1"/>
-    <col min="76" max="76" width="12.125" style="7" customWidth="1"/>
-    <col min="77" max="82" width="9" style="7"/>
-    <col min="83" max="83" width="9" style="6"/>
-    <col min="84" max="85" width="11.125" style="5" customWidth="1"/>
+    <col min="14" max="16" width="12.75" customWidth="1"/>
+    <col min="19" max="19" width="11.5" customWidth="1"/>
+    <col min="20" max="20" width="12.125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="14.375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="15.375" customWidth="1"/>
+    <col min="23" max="23" width="15.875" customWidth="1"/>
+    <col min="24" max="24" width="11" customWidth="1"/>
+    <col min="25" max="25" width="12" style="3" customWidth="1"/>
+    <col min="26" max="26" width="16.625" customWidth="1"/>
+    <col min="27" max="27" width="5.875" customWidth="1"/>
+    <col min="28" max="28" width="9.75" customWidth="1"/>
+    <col min="29" max="29" width="15.125" style="4" customWidth="1"/>
+    <col min="30" max="30" width="15" style="2" customWidth="1"/>
+    <col min="31" max="31" width="14.875" style="2" customWidth="1"/>
+    <col min="32" max="32" width="8.75" style="2" customWidth="1"/>
+    <col min="33" max="33" width="15.25" style="2" customWidth="1"/>
+    <col min="34" max="34" width="16.75" style="2" customWidth="1"/>
+    <col min="35" max="35" width="14" style="2" customWidth="1"/>
+    <col min="36" max="36" width="11.5" style="5"/>
+    <col min="37" max="37" width="13" style="6" customWidth="1"/>
+    <col min="38" max="38" width="12.25" style="6" customWidth="1"/>
+    <col min="39" max="39" width="11.125" style="6" customWidth="1"/>
+    <col min="40" max="40" width="13.625" style="6" customWidth="1"/>
+    <col min="41" max="41" width="12.625" style="6" customWidth="1"/>
+    <col min="42" max="42" width="14.25" style="3" customWidth="1"/>
+    <col min="43" max="43" width="14.5" style="3" customWidth="1"/>
+    <col min="44" max="44" width="12" style="3" customWidth="1"/>
+    <col min="45" max="45" width="10.75" style="6" customWidth="1"/>
+    <col min="47" max="47" width="10.75" customWidth="1"/>
+    <col min="48" max="48" width="16.375" customWidth="1"/>
+    <col min="49" max="49" width="12.375" customWidth="1"/>
+    <col min="50" max="50" width="11.5" style="6" customWidth="1"/>
+    <col min="51" max="51" width="15.875" style="2" customWidth="1"/>
+    <col min="52" max="52" width="11.625" style="6" customWidth="1"/>
+    <col min="53" max="53" width="15.875" style="2" customWidth="1"/>
+    <col min="54" max="54" width="13.5" style="6" customWidth="1"/>
+    <col min="56" max="56" width="11.75" customWidth="1"/>
+    <col min="57" max="57" width="12" customWidth="1"/>
+    <col min="58" max="58" width="11" style="3" customWidth="1"/>
+    <col min="59" max="59" width="9.125" customWidth="1"/>
+    <col min="60" max="60" width="21.5" customWidth="1"/>
+    <col min="61" max="61" width="10.25" customWidth="1"/>
+    <col min="62" max="62" width="9.375" customWidth="1"/>
+    <col min="63" max="63" width="12.75" customWidth="1"/>
+    <col min="64" max="66" width="12.75" style="2" customWidth="1"/>
+    <col min="67" max="67" width="13.75" customWidth="1"/>
+    <col min="68" max="68" width="13.375" customWidth="1"/>
+    <col min="69" max="69" width="11.75" customWidth="1"/>
+    <col min="70" max="70" width="9.875" customWidth="1"/>
+    <col min="71" max="71" width="10" customWidth="1"/>
+    <col min="72" max="72" width="11" customWidth="1"/>
+    <col min="73" max="73" width="9.375"/>
+    <col min="75" max="75" width="11.875" style="7" customWidth="1"/>
+    <col min="76" max="76" width="12.5" style="7" customWidth="1"/>
+    <col min="77" max="77" width="12.125" style="7" customWidth="1"/>
+    <col min="78" max="83" width="9" style="7"/>
+    <col min="84" max="84" width="9" style="6"/>
+    <col min="85" max="86" width="11.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:85">
+    <row r="1" s="1" customFormat="1" spans="1:86">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1499,13 +1502,13 @@
       <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="10" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="8" t="s">
@@ -1514,10 +1517,10 @@
       <c r="W1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="X1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="11" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="8" t="s">
@@ -1526,10 +1529,10 @@
       <c r="AA1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="12" t="s">
+      <c r="AB1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AC1" s="12" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="10" t="s">
@@ -1547,10 +1550,10 @@
       <c r="AH1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="13" t="s">
+      <c r="AI1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="14" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>35</v>
       </c>
       <c r="AK1" s="14" t="s">
@@ -1562,10 +1565,10 @@
       <c r="AM1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="15" t="s">
+      <c r="AN1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
+      <c r="AO1" s="15" t="s">
         <v>40</v>
       </c>
       <c r="AP1" s="11" t="s">
@@ -1574,10 +1577,10 @@
       <c r="AQ1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="14" t="s">
+      <c r="AR1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="8" t="s">
+      <c r="AS1" s="14" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="8" t="s">
@@ -1589,22 +1592,22 @@
       <c r="AV1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="14" t="s">
+      <c r="AW1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="10" t="s">
+      <c r="AX1" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="14" t="s">
+      <c r="AY1" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="10" t="s">
+      <c r="AZ1" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="14" t="s">
+      <c r="BA1" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="8" t="s">
+      <c r="BB1" s="14" t="s">
         <v>53</v>
       </c>
       <c r="BC1" s="8" t="s">
@@ -1613,10 +1616,10 @@
       <c r="BD1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="11" t="s">
+      <c r="BE1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="8" t="s">
+      <c r="BF1" s="11" t="s">
         <v>57</v>
       </c>
       <c r="BG1" s="8" t="s">
@@ -1631,7 +1634,7 @@
       <c r="BJ1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="10" t="s">
+      <c r="BK1" s="8" t="s">
         <v>62</v>
       </c>
       <c r="BL1" s="10" t="s">
@@ -1640,7 +1643,7 @@
       <c r="BM1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="8" t="s">
+      <c r="BN1" s="10" t="s">
         <v>65</v>
       </c>
       <c r="BO1" s="8" t="s">
@@ -1652,10 +1655,10 @@
       <c r="BQ1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="16" t="s">
+      <c r="BR1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="8" t="s">
+      <c r="BS1" s="16" t="s">
         <v>70</v>
       </c>
       <c r="BT1" s="8" t="s">
@@ -1664,7 +1667,7 @@
       <c r="BU1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="17" t="s">
+      <c r="BV1" s="8" t="s">
         <v>73</v>
       </c>
       <c r="BW1" s="17" t="s">
@@ -1691,14 +1694,17 @@
       <c r="CD1" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="14" t="s">
+      <c r="CE1" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="13" t="s">
+      <c r="CF1" s="14" t="s">
         <v>83</v>
       </c>
       <c r="CG1" s="13" t="s">
         <v>84</v>
+      </c>
+      <c r="CH1" s="13" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1706,51 +1712,51 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AH2:AH1048576 AZ2:AZ1048576 BM$1:BM$1048576 BX2:BY1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 AI2:AI1048576 BA2:BA1048576 BN$1:BN$1048576 BY2:BZ1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 AD2:AE1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 AE2:AF1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576 AQ$1:AQ$1048576 BE2:BE1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y$1:Y$1048576 AR$1:AR$1048576 BF2:BF1048576">
       <formula1>1</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576 AF2:AF1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 AG2:AG1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 CB2:CB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 CC2:CC1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576 BZ2:BZ1048576 BV2:BW1048576 CC2:CD1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576 CA2:CA1048576 BW2:BX1048576 CD2:CE1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ$1:AJ$1048576 AN$1:AN$1048576 AW2:AW1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AO$1:AO$1048576 AX2:AX1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR$1:AR$1048576 AK$1:AM$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS$1:AS$1048576 AL$1:AN$1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576 CA2:CA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576 CB2:CB1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576 CE$1:CE$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB2:BB1048576 CF$1:CF$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO$1:AP$1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP$1:AQ$1048576">
       <formula1>32874</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
@@ -1759,7 +1765,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AY2:AY1048565" listDataValidation="1"/>
+    <ignoredError sqref="AZ2:AZ1048565" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -1387,7 +1387,9 @@
     <col min="11" max="11" width="12.375" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="7.75" customWidth="1"/>
-    <col min="14" max="16" width="12.75" customWidth="1"/>
+    <col min="14" max="14" width="12.75" customWidth="1"/>
+    <col min="15" max="15" width="7.625" customWidth="1"/>
+    <col min="16" max="16" width="12.75" customWidth="1"/>
     <col min="19" max="19" width="11.5" customWidth="1"/>
     <col min="20" max="20" width="12.125" style="2" customWidth="1"/>
     <col min="21" max="21" width="14.375" style="2" customWidth="1"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productUpdateNotApproveTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>spu</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>单位</t>
+  </si>
+  <si>
+    <t>产品质保期</t>
   </si>
   <si>
     <t>主要材质</t>
@@ -1377,7 +1380,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CH1"/>
+  <dimension ref="A1:CI1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -1399,57 +1402,58 @@
     <col min="25" max="25" width="12" style="3" customWidth="1"/>
     <col min="26" max="26" width="16.625" customWidth="1"/>
     <col min="27" max="27" width="5.875" customWidth="1"/>
-    <col min="28" max="28" width="9.75" customWidth="1"/>
-    <col min="29" max="29" width="15.125" style="4" customWidth="1"/>
-    <col min="30" max="30" width="15" style="2" customWidth="1"/>
-    <col min="31" max="31" width="14.875" style="2" customWidth="1"/>
-    <col min="32" max="32" width="8.75" style="2" customWidth="1"/>
-    <col min="33" max="33" width="15.25" style="2" customWidth="1"/>
-    <col min="34" max="34" width="16.75" style="2" customWidth="1"/>
-    <col min="35" max="35" width="14" style="2" customWidth="1"/>
-    <col min="36" max="36" width="11.5" style="5"/>
-    <col min="37" max="37" width="13" style="6" customWidth="1"/>
-    <col min="38" max="38" width="12.25" style="6" customWidth="1"/>
-    <col min="39" max="39" width="11.125" style="6" customWidth="1"/>
-    <col min="40" max="40" width="13.625" style="6" customWidth="1"/>
-    <col min="41" max="41" width="12.625" style="6" customWidth="1"/>
-    <col min="42" max="42" width="14.25" style="3" customWidth="1"/>
-    <col min="43" max="43" width="14.5" style="3" customWidth="1"/>
-    <col min="44" max="44" width="12" style="3" customWidth="1"/>
-    <col min="45" max="45" width="10.75" style="6" customWidth="1"/>
-    <col min="47" max="47" width="10.75" customWidth="1"/>
-    <col min="48" max="48" width="16.375" customWidth="1"/>
-    <col min="49" max="49" width="12.375" customWidth="1"/>
-    <col min="50" max="50" width="11.5" style="6" customWidth="1"/>
-    <col min="51" max="51" width="15.875" style="2" customWidth="1"/>
-    <col min="52" max="52" width="11.625" style="6" customWidth="1"/>
-    <col min="53" max="53" width="15.875" style="2" customWidth="1"/>
-    <col min="54" max="54" width="13.5" style="6" customWidth="1"/>
-    <col min="56" max="56" width="11.75" customWidth="1"/>
-    <col min="57" max="57" width="12" customWidth="1"/>
-    <col min="58" max="58" width="11" style="3" customWidth="1"/>
-    <col min="59" max="59" width="9.125" customWidth="1"/>
-    <col min="60" max="60" width="21.5" customWidth="1"/>
-    <col min="61" max="61" width="10.25" customWidth="1"/>
-    <col min="62" max="62" width="9.375" customWidth="1"/>
-    <col min="63" max="63" width="12.75" customWidth="1"/>
-    <col min="64" max="66" width="12.75" style="2" customWidth="1"/>
-    <col min="67" max="67" width="13.75" customWidth="1"/>
-    <col min="68" max="68" width="13.375" customWidth="1"/>
-    <col min="69" max="69" width="11.75" customWidth="1"/>
-    <col min="70" max="70" width="9.875" customWidth="1"/>
-    <col min="71" max="71" width="10" customWidth="1"/>
-    <col min="72" max="72" width="11" customWidth="1"/>
-    <col min="73" max="73" width="9.375"/>
-    <col min="75" max="75" width="11.875" style="7" customWidth="1"/>
-    <col min="76" max="76" width="12.5" style="7" customWidth="1"/>
-    <col min="77" max="77" width="12.125" style="7" customWidth="1"/>
-    <col min="78" max="83" width="9" style="7"/>
-    <col min="84" max="84" width="9" style="6"/>
-    <col min="85" max="86" width="11.125" style="5" customWidth="1"/>
+    <col min="28" max="28" width="10.5" customWidth="1"/>
+    <col min="29" max="29" width="9.75" customWidth="1"/>
+    <col min="30" max="30" width="15.125" style="4" customWidth="1"/>
+    <col min="31" max="31" width="15" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.875" style="2" customWidth="1"/>
+    <col min="33" max="33" width="8.75" style="2" customWidth="1"/>
+    <col min="34" max="34" width="15.25" style="2" customWidth="1"/>
+    <col min="35" max="35" width="16.75" style="2" customWidth="1"/>
+    <col min="36" max="36" width="14" style="2" customWidth="1"/>
+    <col min="37" max="37" width="11.5" style="5"/>
+    <col min="38" max="38" width="13" style="6" customWidth="1"/>
+    <col min="39" max="39" width="12.25" style="6" customWidth="1"/>
+    <col min="40" max="40" width="11.125" style="6" customWidth="1"/>
+    <col min="41" max="41" width="13.625" style="6" customWidth="1"/>
+    <col min="42" max="42" width="12.625" style="6" customWidth="1"/>
+    <col min="43" max="43" width="14.25" style="3" customWidth="1"/>
+    <col min="44" max="44" width="14.5" style="3" customWidth="1"/>
+    <col min="45" max="45" width="12" style="3" customWidth="1"/>
+    <col min="46" max="46" width="10.75" style="6" customWidth="1"/>
+    <col min="48" max="48" width="10.75" customWidth="1"/>
+    <col min="49" max="49" width="16.375" customWidth="1"/>
+    <col min="50" max="50" width="12.375" customWidth="1"/>
+    <col min="51" max="51" width="11.5" style="6" customWidth="1"/>
+    <col min="52" max="52" width="15.875" style="2" customWidth="1"/>
+    <col min="53" max="53" width="11.625" style="6" customWidth="1"/>
+    <col min="54" max="54" width="15.875" style="2" customWidth="1"/>
+    <col min="55" max="55" width="13.5" style="6" customWidth="1"/>
+    <col min="57" max="57" width="11.75" customWidth="1"/>
+    <col min="58" max="58" width="12" customWidth="1"/>
+    <col min="59" max="59" width="11" style="3" customWidth="1"/>
+    <col min="60" max="60" width="9.125" customWidth="1"/>
+    <col min="61" max="61" width="21.5" customWidth="1"/>
+    <col min="62" max="62" width="10.25" customWidth="1"/>
+    <col min="63" max="63" width="9.375" customWidth="1"/>
+    <col min="64" max="64" width="12.75" customWidth="1"/>
+    <col min="65" max="67" width="12.75" style="2" customWidth="1"/>
+    <col min="68" max="68" width="13.75" customWidth="1"/>
+    <col min="69" max="69" width="13.375" customWidth="1"/>
+    <col min="70" max="70" width="11.75" customWidth="1"/>
+    <col min="71" max="71" width="9.875" customWidth="1"/>
+    <col min="72" max="72" width="10" customWidth="1"/>
+    <col min="73" max="73" width="11" customWidth="1"/>
+    <col min="74" max="74" width="9.375"/>
+    <col min="76" max="76" width="11.875" style="7" customWidth="1"/>
+    <col min="77" max="77" width="12.5" style="7" customWidth="1"/>
+    <col min="78" max="78" width="12.125" style="7" customWidth="1"/>
+    <col min="79" max="84" width="9" style="7"/>
+    <col min="85" max="85" width="9" style="6"/>
+    <col min="86" max="87" width="11.125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:86">
+    <row r="1" s="1" customFormat="1" spans="1:87">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1534,10 +1538,10 @@
       <c r="AB1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="12" t="s">
+      <c r="AC1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AD1" s="12" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="10" t="s">
@@ -1555,10 +1559,10 @@
       <c r="AI1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="13" t="s">
+      <c r="AJ1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="14" t="s">
+      <c r="AK1" s="13" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="14" t="s">
@@ -1570,10 +1574,10 @@
       <c r="AN1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="15" t="s">
+      <c r="AO1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="11" t="s">
+      <c r="AP1" s="15" t="s">
         <v>41</v>
       </c>
       <c r="AQ1" s="11" t="s">
@@ -1582,10 +1586,10 @@
       <c r="AR1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="14" t="s">
+      <c r="AS1" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="8" t="s">
+      <c r="AT1" s="14" t="s">
         <v>45</v>
       </c>
       <c r="AU1" s="8" t="s">
@@ -1597,22 +1601,22 @@
       <c r="AW1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="14" t="s">
+      <c r="AX1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="10" t="s">
+      <c r="AY1" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="14" t="s">
+      <c r="AZ1" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="10" t="s">
+      <c r="BA1" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="14" t="s">
+      <c r="BB1" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="8" t="s">
+      <c r="BC1" s="14" t="s">
         <v>54</v>
       </c>
       <c r="BD1" s="8" t="s">
@@ -1621,10 +1625,10 @@
       <c r="BE1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="11" t="s">
+      <c r="BF1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="8" t="s">
+      <c r="BG1" s="11" t="s">
         <v>58</v>
       </c>
       <c r="BH1" s="8" t="s">
@@ -1639,7 +1643,7 @@
       <c r="BK1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="10" t="s">
+      <c r="BL1" s="8" t="s">
         <v>63</v>
       </c>
       <c r="BM1" s="10" t="s">
@@ -1648,7 +1652,7 @@
       <c r="BN1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="8" t="s">
+      <c r="BO1" s="10" t="s">
         <v>66</v>
       </c>
       <c r="BP1" s="8" t="s">
@@ -1660,10 +1664,10 @@
       <c r="BR1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="16" t="s">
+      <c r="BS1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="8" t="s">
+      <c r="BT1" s="16" t="s">
         <v>71</v>
       </c>
       <c r="BU1" s="8" t="s">
@@ -1672,7 +1676,7 @@
       <c r="BV1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="17" t="s">
+      <c r="BW1" s="8" t="s">
         <v>74</v>
       </c>
       <c r="BX1" s="17" t="s">
@@ -1699,14 +1703,17 @@
       <c r="CE1" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="14" t="s">
+      <c r="CF1" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="13" t="s">
+      <c r="CG1" s="14" t="s">
         <v>84</v>
       </c>
       <c r="CH1" s="13" t="s">
         <v>85</v>
+      </c>
+      <c r="CI1" s="13" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1714,51 +1721,51 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 AI2:AI1048576 BA2:BA1048576 BN$1:BN$1048576 BY2:BZ1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 AJ2:AJ1048576 BB2:BB1048576 BO$1:BO$1048576 BZ2:CA1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 AE2:AF1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 AF2:AG1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y$1:Y$1048576 AR$1:AR$1048576 BF2:BF1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y$1:Y$1048576 AS$1:AS$1048576 BG2:BG1048576">
       <formula1>1</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 AG2:AG1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 AH2:AH1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 CC2:CC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576 CD2:CD1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576 CA2:CA1048576 BW2:BX1048576 CD2:CE1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AI1048576 CB2:CB1048576 BX2:BY1048576 CE2:CF1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AO$1:AO$1048576 AX2:AX1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL$1:AL$1048576 AP$1:AP$1048576 AY2:AY1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS$1:AS$1048576 AL$1:AN$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT$1:AT$1048576 AM$1:AO$1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576 CB2:CB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC2:CC1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB2:BB1048576 CF$1:CF$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576 CG$1:CG$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP$1:AQ$1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AR$1048576">
       <formula1>32874</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
@@ -1767,7 +1774,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AZ2:AZ1048565" listDataValidation="1"/>
+    <ignoredError sqref="BA2:BA1048565" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>